--- a/ABA_mining/outputs/eval/task3/check-out/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/check-out/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O2" t="n">
         <v>0.625</v>
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O3" t="n">
         <v>0.625</v>
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O4" t="n">
         <v>0.625</v>
